--- a/分省数据看板（月度）/趋势分析/26年3月.xlsx
+++ b/分省数据看板（月度）/趋势分析/26年3月.xlsx
@@ -27,12 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>名称</t>
   </si>
   <si>
     <t>活跃用户</t>
+  </si>
+  <si>
+    <t>新用户</t>
   </si>
   <si>
     <t>营收</t>
@@ -1084,13 +1087,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="5" max="5" width="12.625"/>
+    <col min="6" max="6" width="12.625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1106,687 +1109,792 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>6184</v>
       </c>
       <c r="C2">
+        <v>2599</v>
+      </c>
+      <c r="D2">
         <v>41608</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>4512</v>
       </c>
-      <c r="E2" s="2">
+      <c r="F2" s="2">
         <v>6.72833117723157</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
         <v>0.729624838292367</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>5487</v>
       </c>
       <c r="C3">
+        <v>1721</v>
+      </c>
+      <c r="D3">
         <v>24137</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>4147</v>
       </c>
-      <c r="E3" s="2">
+      <c r="F3" s="2">
         <v>4.398942956078</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G3" s="1">
         <v>0.755786404228176</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4">
         <v>6739</v>
       </c>
       <c r="C4">
+        <v>3248</v>
+      </c>
+      <c r="D4">
         <v>18485</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>4729</v>
       </c>
-      <c r="E4" s="2">
+      <c r="F4" s="2">
         <v>2.7429885739724</v>
       </c>
-      <c r="F4" s="1">
+      <c r="G4" s="1">
         <v>0.701736162635406</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5">
         <v>5133</v>
       </c>
       <c r="C5">
+        <v>3714</v>
+      </c>
+      <c r="D5">
         <v>8571</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>4094</v>
       </c>
-      <c r="E5" s="2">
+      <c r="F5" s="2">
         <v>1.6697837521917</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="1">
         <v>0.797584258718099</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>3101</v>
       </c>
       <c r="C6">
+        <v>1481</v>
+      </c>
+      <c r="D6">
         <v>12700</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>2219</v>
       </c>
-      <c r="E6" s="2">
+      <c r="F6" s="2">
         <v>4.09545307965173</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>0.715575620767494</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7">
         <v>9742</v>
       </c>
       <c r="C7">
+        <v>2990</v>
+      </c>
+      <c r="D7">
         <v>49915</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>7375</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>5.12369123383289</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
         <v>0.757031410388011</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>3309</v>
       </c>
       <c r="C8">
+        <v>1340</v>
+      </c>
+      <c r="D8">
         <v>15609</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>2464</v>
       </c>
-      <c r="E8" s="2">
+      <c r="F8" s="2">
         <v>4.71713508612874</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="1">
         <v>0.744635841644001</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>6133</v>
       </c>
       <c r="C9">
+        <v>2149</v>
+      </c>
+      <c r="D9">
         <v>23604</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>4451</v>
       </c>
-      <c r="E9" s="2">
+      <c r="F9" s="2">
         <v>3.8486874286646</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G9" s="1">
         <v>0.72574596445459</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>3171</v>
       </c>
       <c r="C10">
+        <v>1141</v>
+      </c>
+      <c r="D10">
         <v>29247</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>2234</v>
       </c>
-      <c r="E10" s="2">
+      <c r="F10" s="2">
         <v>9.2232734153264</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G10" s="1">
         <v>0.704509618416903</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>17357</v>
       </c>
       <c r="C11">
+        <v>6174</v>
+      </c>
+      <c r="D11">
         <v>109885</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>12476</v>
       </c>
-      <c r="E11" s="2">
+      <c r="F11" s="2">
         <v>6.33087515123581</v>
       </c>
-      <c r="F11" s="1">
+      <c r="G11" s="1">
         <v>0.71878780895316</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>5617</v>
       </c>
       <c r="C12">
+        <v>2266</v>
+      </c>
+      <c r="D12">
         <v>31817</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>3897</v>
       </c>
-      <c r="E12" s="2">
+      <c r="F12" s="2">
         <v>5.66441160761973</v>
       </c>
-      <c r="F12" s="1">
+      <c r="G12" s="1">
         <v>0.693786718889087</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>9939</v>
       </c>
       <c r="C13">
+        <v>3581</v>
+      </c>
+      <c r="D13">
         <v>35133</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>7140</v>
       </c>
-      <c r="E13" s="2">
+      <c r="F13" s="2">
         <v>3.53486266223966</v>
       </c>
-      <c r="F13" s="1">
+      <c r="G13" s="1">
         <v>0.718382130999094</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14">
         <v>7996</v>
       </c>
       <c r="C14">
+        <v>2784</v>
+      </c>
+      <c r="D14">
         <v>35129</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>5767</v>
       </c>
-      <c r="E14" s="2">
+      <c r="F14" s="2">
         <v>4.39332166083042</v>
       </c>
-      <c r="F14" s="1">
+      <c r="G14" s="1">
         <v>0.721235617808904</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>6217</v>
       </c>
       <c r="C15">
+        <v>2862</v>
+      </c>
+      <c r="D15">
         <v>15337</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>4414</v>
       </c>
-      <c r="E15" s="2">
+      <c r="F15" s="2">
         <v>2.46694547209265</v>
       </c>
-      <c r="F15" s="1">
+      <c r="G15" s="1">
         <v>0.709988740550105</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16">
         <v>20984</v>
       </c>
       <c r="C16">
+        <v>7121</v>
+      </c>
+      <c r="D16">
         <v>71909</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>15713</v>
       </c>
-      <c r="E16" s="2">
+      <c r="F16" s="2">
         <v>3.42684902783073</v>
       </c>
-      <c r="F16" s="1">
+      <c r="G16" s="1">
         <v>0.748808616088448</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17">
         <v>7525</v>
       </c>
       <c r="C17">
+        <v>3528</v>
+      </c>
+      <c r="D17">
         <v>17954</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>5099</v>
       </c>
-      <c r="E17" s="2">
+      <c r="F17" s="2">
         <v>2.38591362126246</v>
       </c>
-      <c r="F17" s="1">
+      <c r="G17" s="1">
         <v>0.677607973421927</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18">
         <v>6329</v>
       </c>
       <c r="C18">
+        <v>2479</v>
+      </c>
+      <c r="D18">
         <v>24526</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>4461</v>
       </c>
-      <c r="E18" s="2">
+      <c r="F18" s="2">
         <v>3.87517775319956</v>
       </c>
-      <c r="F18" s="1">
+      <c r="G18" s="1">
         <v>0.704850687312372</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19">
         <v>7371</v>
       </c>
       <c r="C19">
+        <v>3048</v>
+      </c>
+      <c r="D19">
         <v>34656</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>5291</v>
       </c>
-      <c r="E19" s="2">
+      <c r="F19" s="2">
         <v>4.7016687016687</v>
       </c>
-      <c r="F19" s="1">
+      <c r="G19" s="1">
         <v>0.717813051146384</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20">
         <v>13533</v>
       </c>
       <c r="C20">
+        <v>5422</v>
+      </c>
+      <c r="D20">
         <v>62369</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>9479</v>
       </c>
-      <c r="E20" s="2">
+      <c r="F20" s="2">
         <v>4.60866031183034</v>
       </c>
-      <c r="F20" s="1">
+      <c r="G20" s="1">
         <v>0.700435971329343</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21">
         <v>2540</v>
       </c>
       <c r="C21">
+        <v>1238</v>
+      </c>
+      <c r="D21">
         <v>7433</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>1730</v>
       </c>
-      <c r="E21" s="2">
+      <c r="F21" s="2">
         <v>2.92637795275591</v>
       </c>
-      <c r="F21" s="1">
+      <c r="G21" s="1">
         <v>0.681102362204724</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B22">
         <v>1189</v>
       </c>
       <c r="C22">
+        <v>486</v>
+      </c>
+      <c r="D22">
         <v>3886</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>822</v>
       </c>
-      <c r="E22" s="2">
+      <c r="F22" s="2">
         <v>3.26829268292683</v>
       </c>
-      <c r="F22" s="1">
+      <c r="G22" s="1">
         <v>0.691337258200168</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23">
         <v>4398</v>
       </c>
       <c r="C23">
+        <v>1684</v>
+      </c>
+      <c r="D23">
         <v>22422</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>3061</v>
       </c>
-      <c r="E23" s="2">
+      <c r="F23" s="2">
         <v>5.09822646657572</v>
       </c>
-      <c r="F23" s="1">
+      <c r="G23" s="1">
         <v>0.69599818099136</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B24">
         <v>5813</v>
       </c>
       <c r="C24">
+        <v>2410</v>
+      </c>
+      <c r="D24">
         <v>21415</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>4103</v>
       </c>
-      <c r="E24" s="2">
+      <c r="F24" s="2">
         <v>3.68398417340444</v>
       </c>
-      <c r="F24" s="1">
+      <c r="G24" s="1">
         <v>0.705831756408051</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B25">
         <v>2184</v>
       </c>
       <c r="C25">
+        <v>1092</v>
+      </c>
+      <c r="D25">
         <v>5547</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>1448</v>
       </c>
-      <c r="E25" s="2">
+      <c r="F25" s="2">
         <v>2.53983516483516</v>
       </c>
-      <c r="F25" s="1">
+      <c r="G25" s="1">
         <v>0.663003663003663</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26">
         <v>2519</v>
       </c>
       <c r="C26">
+        <v>1260</v>
+      </c>
+      <c r="D26">
         <v>12350</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>1605</v>
       </c>
-      <c r="E26" s="2">
+      <c r="F26" s="2">
         <v>4.90273918221517</v>
       </c>
-      <c r="F26" s="1">
+      <c r="G26" s="1">
         <v>0.637157602223104</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27">
         <v>173</v>
       </c>
       <c r="C27">
+        <v>97</v>
+      </c>
+      <c r="D27">
         <v>1105</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>116</v>
       </c>
-      <c r="E27" s="2">
+      <c r="F27" s="2">
         <v>6.38728323699422</v>
       </c>
-      <c r="F27" s="1">
+      <c r="G27" s="1">
         <v>0.670520231213873</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28">
         <v>3842</v>
       </c>
       <c r="C28">
+        <v>1930</v>
+      </c>
+      <c r="D28">
         <v>12547</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>2612</v>
       </c>
-      <c r="E28" s="2">
+      <c r="F28" s="2">
         <v>3.26574700676731</v>
       </c>
-      <c r="F28" s="1">
+      <c r="G28" s="1">
         <v>0.679854242581989</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29">
         <v>2580</v>
       </c>
       <c r="C29">
+        <v>1317</v>
+      </c>
+      <c r="D29">
         <v>6616</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>1846</v>
       </c>
-      <c r="E29" s="2">
+      <c r="F29" s="2">
         <v>2.56434108527132</v>
       </c>
-      <c r="F29" s="1">
+      <c r="G29" s="1">
         <v>0.715503875968992</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30">
         <v>643</v>
       </c>
       <c r="C30">
+        <v>311</v>
+      </c>
+      <c r="D30">
         <v>2389</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>453</v>
       </c>
-      <c r="E30" s="2">
+      <c r="F30" s="2">
         <v>3.7153965785381</v>
       </c>
-      <c r="F30" s="1">
+      <c r="G30" s="1">
         <v>0.704510108864697</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B31">
         <v>1029</v>
       </c>
       <c r="C31">
+        <v>460</v>
+      </c>
+      <c r="D31">
         <v>1943</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>730</v>
       </c>
-      <c r="E31" s="2">
+      <c r="F31" s="2">
         <v>1.88824101068999</v>
       </c>
-      <c r="F31" s="1">
+      <c r="G31" s="1">
         <v>0.709426627793975</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B32">
         <v>3406</v>
       </c>
       <c r="C32">
+        <v>1596</v>
+      </c>
+      <c r="D32">
         <v>8076</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <v>2229</v>
       </c>
-      <c r="E32" s="2">
+      <c r="F32" s="2">
         <v>2.37110980622431</v>
       </c>
-      <c r="F32" s="1">
+      <c r="G32" s="1">
         <v>0.654433352906635</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B33">
         <v>16</v>
       </c>
       <c r="C33">
+        <v>10</v>
+      </c>
+      <c r="D33">
         <v>49</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>15</v>
       </c>
-      <c r="E33" s="2">
+      <c r="F33" s="2">
         <v>3.0625</v>
       </c>
-      <c r="F33" s="1">
+      <c r="G33" s="1">
         <v>0.9375</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B34">
         <v>11</v>
       </c>
       <c r="C34">
+        <v>6</v>
+      </c>
+      <c r="D34">
         <v>49</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>6</v>
       </c>
-      <c r="E34" s="2">
+      <c r="F34" s="2">
         <v>4.45454545454545</v>
       </c>
-      <c r="F34" s="1">
+      <c r="G34" s="1">
         <v>0.545454545454545</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B35">
         <v>14</v>
       </c>
       <c r="C35">
+        <v>10</v>
+      </c>
+      <c r="D35">
         <v>0</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>11</v>
       </c>
-      <c r="E35" s="2">
+      <c r="F35" s="2">
         <v>0</v>
       </c>
-      <c r="F35" s="1">
+      <c r="G35" s="1">
         <v>0.785714285714286</v>
       </c>
     </row>
